--- a/database/DanhSach.xlsx
+++ b/database/DanhSach.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="DiemDanh" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,7 +397,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:N2"/>
+  <cols>
+    <col min="1" max="1" width="10.83203125" customWidth="1"/>
+    <col min="2" max="2" width="11.83203125" customWidth="1"/>
+    <col min="3" max="3" width="18.83203125" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" customWidth="1"/>
+    <col min="8" max="8" width="10.83203125" customWidth="1"/>
+    <col min="9" max="9" width="10.83203125" customWidth="1"/>
+    <col min="10" max="10" width="10.83203125" customWidth="1"/>
+    <col min="11" max="11" width="10.83203125" customWidth="1"/>
+    <col min="12" max="12" width="10.83203125" customWidth="1"/>
+    <col min="13" max="13" width="10.83203125" customWidth="1"/>
+    <col min="14" max="14" width="10.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -410,19 +426,37 @@
         <v>Họ tên</v>
       </c>
       <c r="D1" t="str">
-        <v>04/09</v>
+        <v>02/09</v>
       </c>
       <c r="E1" t="str">
-        <v>11/09</v>
+        <v>09/09</v>
       </c>
       <c r="F1" t="str">
-        <v>18/09</v>
+        <v>16/09</v>
       </c>
       <c r="G1" t="str">
-        <v>25/09</v>
+        <v>23/09</v>
       </c>
       <c r="H1" t="str">
-        <v>02/10</v>
+        <v>30/09</v>
+      </c>
+      <c r="I1" t="str">
+        <v>07/10</v>
+      </c>
+      <c r="J1" t="str">
+        <v>14/10</v>
+      </c>
+      <c r="K1" t="str">
+        <v>21/10</v>
+      </c>
+      <c r="L1" t="str">
+        <v>28/10</v>
+      </c>
+      <c r="M1" t="str">
+        <v>04/11</v>
+      </c>
+      <c r="N1" t="str">
+        <v>% CC</v>
       </c>
     </row>
     <row r="2">
@@ -436,24 +470,42 @@
         <v>Nguyễn Đức Trọng</v>
       </c>
       <c r="D2" t="str">
-        <v>present</v>
+        <v>Có mặt</v>
       </c>
       <c r="E2" t="str">
-        <v>present</v>
+        <v>Có mặt</v>
       </c>
       <c r="F2" t="str">
-        <v>present</v>
+        <v>Có mặt</v>
       </c>
       <c r="G2" t="str">
-        <v>present</v>
+        <v>Có mặt</v>
       </c>
       <c r="H2" t="str">
-        <v>present</v>
+        <v>Có mặt</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Có mặt</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Có mặt</v>
+      </c>
+      <c r="K2" t="str">
+        <v>Có mặt</v>
+      </c>
+      <c r="L2" t="str">
+        <v>Có mặt</v>
+      </c>
+      <c r="M2" t="str">
+        <v>Có mặt</v>
+      </c>
+      <c r="N2" t="str">
+        <v>100%</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N2"/>
   </ignoredErrors>
 </worksheet>
 </file>